--- a/artfynd/A 20477-2019 artfynd.xlsx
+++ b/artfynd/A 20477-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20477-2019 artfynd.xlsx
+++ b/artfynd/A 20477-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1242,6 +1242,117 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120288138</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91128</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>760</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Pålkem, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>792682</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7374491</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20477-2019 artfynd.xlsx
+++ b/artfynd/A 20477-2019 artfynd.xlsx
@@ -1247,7 +1247,7 @@
         <v>120288138</v>
       </c>
       <c r="B7" t="n">
-        <v>91128</v>
+        <v>91146</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 20477-2019 artfynd.xlsx
+++ b/artfynd/A 20477-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112605437</v>
+        <v>120288138</v>
       </c>
       <c r="B5" t="n">
-        <v>77856</v>
+        <v>91198</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,41 +1042,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pålkem, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>793688</v>
+        <v>792682</v>
       </c>
       <c r="R5" t="n">
-        <v>7373825</v>
+        <v>7374491</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,17 +1104,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,224 +1138,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>112605482</v>
-      </c>
-      <c r="B6" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Pålkem, Nb</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>792462</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7374719</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>120288138</v>
-      </c>
-      <c r="B7" t="n">
-        <v>91198</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>760</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Doftticka</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Haploporus odorus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Pålkem, Nb</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>792682</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7374491</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
